--- a/tests/agent_contract/data/H5_nested_group.xlsx
+++ b/tests/agent_contract/data/H5_nested_group.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +413,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>年份</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2023</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1798</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +471,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2789</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +489,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2309</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +507,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +525,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3290</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +561,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2097</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +579,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3263</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +597,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1558</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +615,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1580</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="12">
@@ -622,7 +633,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2421</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="13">
@@ -640,7 +651,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1693</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="14">
@@ -658,7 +669,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1453</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="15">
@@ -676,7 +687,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="16">
@@ -694,7 +705,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="17">
@@ -708,11 +719,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2681</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="18">
@@ -730,7 +741,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3433</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="19">
@@ -748,7 +759,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3223</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="20">
@@ -766,7 +777,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1951</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="21">
@@ -784,7 +795,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3457</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="22">
@@ -802,7 +813,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1531</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +831,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2309</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="24">
@@ -838,7 +849,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1917</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="25">
@@ -856,7 +867,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1455</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="26">
@@ -874,7 +885,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1341</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="27">
@@ -892,7 +903,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1432</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="28">
@@ -910,7 +921,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1231</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="29">
@@ -928,7 +939,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1236</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="30">
@@ -942,11 +953,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1200</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="31">
@@ -960,11 +971,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1203</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="32">
@@ -978,11 +989,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1200</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="33">
@@ -996,11 +1007,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1200</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="34">
@@ -1018,7 +1029,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2012</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="35">
@@ -1036,7 +1047,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2977</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="36">
@@ -1054,7 +1065,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2735</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="37">
@@ -1072,7 +1083,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1415</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="38">
@@ -1090,7 +1101,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2277</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="39">
@@ -1108,7 +1119,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2187</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="40">
@@ -1126,7 +1137,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3368</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="41">
@@ -1144,7 +1155,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2194</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="42">
@@ -1162,7 +1173,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2761</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="43">
@@ -1180,7 +1191,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2813</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="44">
@@ -1198,7 +1209,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1704</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="45">
@@ -1216,7 +1227,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1235</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="46">
@@ -1234,7 +1245,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1211</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="47">
@@ -1252,7 +1263,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1245</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="48">
@@ -1270,7 +1281,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1231</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="49">
@@ -1279,16 +1290,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1232</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="50">
@@ -1297,16 +1308,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1203</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="51">
@@ -1315,16 +1326,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1200</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="52">
@@ -1342,7 +1353,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3048</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="53">
@@ -1360,7 +1371,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1660</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="54">
@@ -1378,7 +1389,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2954</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="55">
@@ -1396,7 +1407,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2599</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="56">
@@ -1414,7 +1425,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2801</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="57">
@@ -1432,7 +1443,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2215</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="58">
@@ -1450,7 +1461,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3300</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="59">
@@ -1468,7 +1479,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1702</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="60">
@@ -1486,7 +1497,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2528</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="61">
@@ -1504,7 +1515,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2207</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="62">
@@ -1522,7 +1533,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1494</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="63">
@@ -1540,7 +1551,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2296</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="64">
@@ -1558,7 +1569,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1442</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="65">
@@ -1576,7 +1587,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1534</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="66">
@@ -1594,7 +1605,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1328</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="67">
@@ -1608,11 +1619,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1254</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="68">
@@ -1626,11 +1637,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1232</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="69">
@@ -1644,11 +1655,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1200</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="70">
@@ -1662,11 +1673,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1206</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="71">
@@ -1684,7 +1695,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1900</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="72">
@@ -1702,7 +1713,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2383</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="73">
@@ -1720,7 +1731,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3472</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="74">
@@ -1738,7 +1749,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3259</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="75">
@@ -1756,7 +1767,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1744</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="76">
@@ -1774,7 +1785,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2271</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="77">
@@ -1792,7 +1803,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1746</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="78">
@@ -1810,7 +1821,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2899</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="79">
@@ -1828,7 +1839,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1518</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="80">
@@ -1846,7 +1857,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2798</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="81">
@@ -1864,7 +1875,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2754</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="82">
@@ -1882,7 +1893,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1415</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="83">
@@ -1900,7 +1911,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2993</v>
+        <v>4986</v>
       </c>
     </row>
     <row r="84">
@@ -1914,11 +1925,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10848</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="85">
@@ -1936,7 +1947,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2478</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="86">
@@ -1954,7 +1965,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1609</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="87">
@@ -1972,7 +1983,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1487</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="88">
@@ -1990,7 +2001,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2652</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="89">
@@ -2008,7 +2019,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2749</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="90">
@@ -2026,7 +2037,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2137</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="91">
@@ -2044,7 +2055,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1643</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="92">
@@ -2062,7 +2073,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3117</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="93">
@@ -2080,7 +2091,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2553</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="94">
@@ -2098,7 +2109,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2957</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="95">
@@ -2116,7 +2127,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2262</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="96">
@@ -2134,7 +2145,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2078</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="97">
@@ -2152,7 +2163,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1449</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="98">
@@ -2170,7 +2181,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1699</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="99">
@@ -2188,7 +2199,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1750</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="100">
@@ -2206,25 +2217,25 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12380</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2287</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="102">
@@ -2242,7 +2253,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1854</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="103">
@@ -2260,7 +2271,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3399</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="104">
@@ -2278,7 +2289,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1233</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="105">
@@ -2296,7 +2307,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2745</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="106">
@@ -2314,7 +2325,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3292</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="107">
@@ -2332,7 +2343,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2330</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="108">
@@ -2350,7 +2361,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2074</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="109">
@@ -2368,7 +2379,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1308</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="110">
@@ -2386,7 +2397,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2199</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="111">
@@ -2404,7 +2415,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2466</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="112">
@@ -2422,7 +2433,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1776</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="113">
@@ -2440,7 +2451,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1715</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="114">
@@ -2458,7 +2469,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1886</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="115">
@@ -2476,7 +2487,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2937</v>
+        <v>22644</v>
       </c>
     </row>
     <row r="116">
@@ -2490,11 +2501,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2478</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="117">
@@ -2508,11 +2519,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>16021</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="118">
@@ -2530,7 +2541,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1884</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="119">
@@ -2548,7 +2559,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2632</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="120">
@@ -2566,7 +2577,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2935</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="121">
@@ -2584,7 +2595,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1414</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="122">
@@ -2602,7 +2613,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3207</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="123">
@@ -2620,7 +2631,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3397</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="124">
@@ -2638,7 +2649,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2089</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="125">
@@ -2656,7 +2667,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3230</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="126">
@@ -2674,7 +2685,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3173</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="127">
@@ -2692,7 +2703,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2780</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="128">
@@ -2710,7 +2721,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2469</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="129">
@@ -2728,7 +2739,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1783</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="130">
@@ -2746,7 +2757,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2206</v>
+        <v>23979</v>
       </c>
     </row>
     <row r="131">
@@ -2760,11 +2771,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1393</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="132">
@@ -2778,11 +2789,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>23408</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="133">
@@ -2800,7 +2811,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2988</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="134">
@@ -2818,7 +2829,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3422</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="135">
@@ -2836,7 +2847,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2259</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="136">
@@ -2854,7 +2865,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3372</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="137">
@@ -2872,7 +2883,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1234</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="138">
@@ -2890,7 +2901,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2483</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="139">
@@ -2908,7 +2919,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3213</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="140">
@@ -2926,7 +2937,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2731</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="141">
@@ -2944,7 +2955,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2583</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="142">
@@ -2962,7 +2973,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2354</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="143">
@@ -2980,7 +2991,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3476</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="144">
@@ -2998,7 +3009,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3157</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="145">
@@ -3016,7 +3027,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2695</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="146">
@@ -3034,7 +3045,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3113</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="147">
@@ -3052,7 +3063,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1922</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="148">
@@ -3070,7 +3081,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3245</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="149">
@@ -3088,7 +3099,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2315</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="150">
@@ -3106,7 +3117,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2006</v>
+        <v>21472</v>
       </c>
     </row>
     <row r="151">
@@ -3115,16 +3126,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>13432</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="152">
@@ -3142,7 +3153,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2271</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="153">
@@ -3160,7 +3171,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3092</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="154">
@@ -3178,7 +3189,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2261</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="155">
@@ -3196,7 +3207,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2671</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="156">
@@ -3214,7 +3225,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2091</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="157">
@@ -3232,7 +3243,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2704</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="158">
@@ -3250,7 +3261,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3095</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="159">
@@ -3268,7 +3279,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1267</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="160">
@@ -3286,7 +3297,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1354</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="161">
@@ -3304,7 +3315,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1794</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="162">
@@ -3322,7 +3333,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1341</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="163">
@@ -3340,7 +3351,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1532</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="164">
@@ -3358,7 +3369,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1923</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="165">
@@ -3376,7 +3387,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3036</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="166">
@@ -3394,7 +3405,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1882</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="167">
@@ -3412,7 +3423,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1317</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="168">
@@ -3430,7 +3441,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3215</v>
+        <v>28472</v>
       </c>
     </row>
     <row r="169">
@@ -3444,11 +3455,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1738</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="170">
@@ -3462,11 +3473,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="171">
@@ -3480,11 +3491,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>26157</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="172">
@@ -3502,7 +3513,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1653</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="173">
@@ -3520,7 +3531,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1370</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="174">
@@ -3538,7 +3549,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1894</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="175">
@@ -3556,7 +3567,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1285</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="176">
@@ -3574,7 +3585,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1702</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="177">
@@ -3592,7 +3603,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2428</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="178">
@@ -3610,7 +3621,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2220</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="179">
@@ -3628,7 +3639,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>3410</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="180">
@@ -3646,7 +3657,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2068</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="181">
@@ -3664,7 +3675,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1663</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="182">
@@ -3682,7 +3693,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1816</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="183">
@@ -3700,7 +3711,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1310</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="184">
@@ -3718,7 +3729,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1417</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="185">
@@ -3736,7 +3747,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2011</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="186">
@@ -3754,7 +3765,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1655</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="187">
@@ -3772,7 +3783,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2900</v>
+        <v>29662</v>
       </c>
     </row>
     <row r="188">
@@ -3786,11 +3797,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1453</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="189">
@@ -3804,11 +3815,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>39745</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="190">
@@ -3826,7 +3837,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1457</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="191">
@@ -3844,7 +3855,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1880</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="192">
@@ -3862,7 +3873,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2939</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="193">
@@ -3880,7 +3891,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3434</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="194">
@@ -3898,7 +3909,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3156</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="195">
@@ -3916,7 +3927,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1560</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="196">
@@ -3934,7 +3945,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2674</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="197">
@@ -3952,7 +3963,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2481</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="198">
@@ -3970,7 +3981,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2016</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="199">
@@ -3988,7 +3999,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>3041</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="200">
@@ -4006,133 +4017,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1452</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>2951</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>2851</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>2549</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>2590</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>33949</v>
+        <v>46437</v>
       </c>
     </row>
   </sheetData>
